--- a/inst/extdata/Example.xlsx
+++ b/inst/extdata/Example.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">TRIAL</t>
   </si>
@@ -32,6 +32,12 @@
     <t xml:space="preserve">SE</t>
   </si>
   <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
     <t xml:space="preserve">ROUND_MEAN</t>
   </si>
   <si>
@@ -96,6 +102,9 @@
   </si>
   <si>
     <t xml:space="preserve">Creat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration</t>
   </si>
 </sst>
 </file>
@@ -467,13 +476,19 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -482,22 +497,24 @@
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2"/>
-      <c r="J2" t="n">
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2" t="n">
         <v>40</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>10</v>
       </c>
-      <c r="L2"/>
-      <c r="M2"/>
       <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
@@ -506,22 +523,24 @@
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
-      <c r="J3" t="n">
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3" t="n">
         <v>34</v>
       </c>
-      <c r="K3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="M3" t="n">
+        <v>16</v>
+      </c>
       <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -532,22 +551,24 @@
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
-      <c r="L4" t="n">
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>8</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -558,22 +579,24 @@
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5" t="n">
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5" t="n">
         <v>7</v>
       </c>
-      <c r="M5" t="n">
-        <v>15</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P5" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
@@ -587,27 +610,29 @@
       <c r="F6" t="n">
         <v>3.36</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
+      <c r="G6"/>
+      <c r="H6"/>
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
       <c r="L6"/>
       <c r="M6"/>
       <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>17</v>
@@ -619,27 +644,29 @@
         <v>12</v>
       </c>
       <c r="F7"/>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
+      <c r="G7"/>
+      <c r="H7"/>
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7"/>
-      <c r="K7"/>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7"/>
       <c r="M7"/>
       <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>15</v>
@@ -651,27 +678,29 @@
         <v>7</v>
       </c>
       <c r="F8"/>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
+      <c r="G8"/>
+      <c r="H8"/>
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8"/>
-      <c r="K8"/>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
       <c r="L8"/>
       <c r="M8"/>
       <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>17</v>
@@ -683,27 +712,29 @@
         <v>7</v>
       </c>
       <c r="F9"/>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
+      <c r="G9"/>
+      <c r="H9"/>
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
       <c r="L9"/>
       <c r="M9"/>
       <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>15</v>
@@ -715,27 +746,29 @@
         <v>100</v>
       </c>
       <c r="F10"/>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
+      <c r="G10"/>
+      <c r="H10"/>
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10"/>
-      <c r="K10"/>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
       <c r="L10"/>
       <c r="M10"/>
       <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>17</v>
@@ -747,27 +780,29 @@
         <v>60</v>
       </c>
       <c r="F11"/>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
+      <c r="G11"/>
+      <c r="H11"/>
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11"/>
-      <c r="K11"/>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
@@ -779,27 +814,29 @@
         <v>5</v>
       </c>
       <c r="F12"/>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
+      <c r="G12"/>
+      <c r="H12"/>
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12"/>
-      <c r="K12"/>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>17</v>
@@ -811,27 +848,29 @@
         <v>7</v>
       </c>
       <c r="F13"/>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
+      <c r="G13"/>
+      <c r="H13"/>
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13"/>
-      <c r="K13"/>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
       <c r="L13"/>
       <c r="M13"/>
       <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>15</v>
@@ -843,27 +882,29 @@
         <v>18</v>
       </c>
       <c r="F14"/>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
+      <c r="G14"/>
+      <c r="H14"/>
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14"/>
-      <c r="K14"/>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>17</v>
@@ -875,27 +916,29 @@
         <v>23</v>
       </c>
       <c r="F15"/>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
+      <c r="G15"/>
+      <c r="H15"/>
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15"/>
-      <c r="K15"/>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
@@ -909,27 +952,29 @@
       <c r="F16" t="n">
         <v>1.5</v>
       </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
+      <c r="G16"/>
+      <c r="H16"/>
       <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="J16"/>
-      <c r="K16"/>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
       <c r="L16"/>
       <c r="M16"/>
       <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -941,27 +986,29 @@
         <v>6.7</v>
       </c>
       <c r="F17"/>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
+      <c r="G17"/>
+      <c r="H17"/>
       <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="J17"/>
-      <c r="K17"/>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
       <c r="L17"/>
       <c r="M17"/>
       <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
         <v>15</v>
@@ -973,27 +1020,29 @@
         <v>11.1</v>
       </c>
       <c r="F18"/>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
+      <c r="G18"/>
+      <c r="H18"/>
       <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="J18"/>
-      <c r="K18"/>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
@@ -1005,27 +1054,29 @@
         <v>5.1</v>
       </c>
       <c r="F19"/>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
+      <c r="G19"/>
+      <c r="H19"/>
       <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="J19"/>
-      <c r="K19"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" t="n">
         <v>15</v>
@@ -1037,27 +1088,29 @@
         <v>7.2</v>
       </c>
       <c r="F20"/>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
+      <c r="G20"/>
+      <c r="H20"/>
       <c r="I20" t="n">
         <v>1</v>
       </c>
-      <c r="J20"/>
-      <c r="K20"/>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
       <c r="L20"/>
       <c r="M20"/>
       <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
         <v>15</v>
@@ -1069,27 +1122,29 @@
         <v>4.1</v>
       </c>
       <c r="F21"/>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
+      <c r="G21"/>
+      <c r="H21"/>
       <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="J21"/>
-      <c r="K21"/>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
       <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
         <v>15</v>
@@ -1101,27 +1156,29 @@
         <v>51</v>
       </c>
       <c r="F22"/>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G22"/>
+      <c r="H22"/>
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22"/>
-      <c r="K22"/>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C23" t="n">
         <v>15</v>
@@ -1133,27 +1190,29 @@
         <v>45</v>
       </c>
       <c r="F23"/>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
+      <c r="G23"/>
+      <c r="H23"/>
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23"/>
-      <c r="K23"/>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
       <c r="L23"/>
       <c r="M23"/>
       <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" t="n">
         <v>15</v>
@@ -1165,27 +1224,29 @@
         <v>10</v>
       </c>
       <c r="F24"/>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
+      <c r="G24"/>
+      <c r="H24"/>
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24"/>
-      <c r="K24"/>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" t="n">
         <v>15</v>
@@ -1197,27 +1258,29 @@
         <v>11</v>
       </c>
       <c r="F25"/>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
+      <c r="G25"/>
+      <c r="H25"/>
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25"/>
-      <c r="K25"/>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
       <c r="L25"/>
       <c r="M25"/>
       <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C26" t="n">
         <v>15</v>
@@ -1229,27 +1292,29 @@
         <v>0.09</v>
       </c>
       <c r="F26"/>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
+      <c r="G26"/>
+      <c r="H26"/>
       <c r="I26" t="n">
         <v>2</v>
       </c>
-      <c r="J26"/>
-      <c r="K26"/>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
       <c r="L26"/>
       <c r="M26"/>
       <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C27" t="n">
         <v>15</v>
@@ -1261,20 +1326,94 @@
         <v>0.12</v>
       </c>
       <c r="F27"/>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
+      <c r="G27"/>
+      <c r="H27"/>
       <c r="I27" t="n">
         <v>2</v>
       </c>
-      <c r="J27"/>
-      <c r="K27"/>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
       <c r="L27"/>
       <c r="M27"/>
       <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>17</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
